--- a/缺料分析0527/缺料分析_0527_5.xlsx
+++ b/缺料分析0527/缺料分析_0527_5.xlsx
@@ -15805,7 +15805,6 @@
       </c>
       <c r="E17" s="4" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="18" customHeight="1" s="21">
       <c r="A19" s="24" t="inlineStr">
         <is>
@@ -17929,7 +17928,6 @@
       </c>
       <c r="E119" s="7" t="n"/>
     </row>
-    <row r="120"/>
     <row r="121" ht="18" customHeight="1" s="21">
       <c r="A121" s="23" t="inlineStr">
         <is>
@@ -18109,7 +18107,6 @@
       </c>
       <c r="E129" s="3" t="n"/>
     </row>
-    <row r="130"/>
     <row r="131" ht="18" customHeight="1" s="21">
       <c r="A131" s="26" t="inlineStr">
         <is>
@@ -18133,7 +18130,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -18158,7 +18155,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -18183,7 +18180,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -18208,7 +18205,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -18233,7 +18230,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -18258,7 +18255,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -18283,7 +18280,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -18308,7 +18305,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -18333,7 +18330,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -18358,7 +18355,7 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -18383,7 +18380,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -18408,7 +18405,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -18433,7 +18430,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -18458,7 +18455,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -18483,7 +18480,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -18508,7 +18505,7 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -18533,7 +18530,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -18558,7 +18555,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -18583,7 +18580,7 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -18608,7 +18605,7 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -18633,7 +18630,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -18658,7 +18655,7 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -18683,7 +18680,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -18708,7 +18705,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -18733,7 +18730,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -18758,7 +18755,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -18783,7 +18780,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -18808,7 +18805,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -18833,7 +18830,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -18858,7 +18855,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -18883,7 +18880,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -18908,7 +18905,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -18933,7 +18930,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -18958,7 +18955,7 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -18983,7 +18980,7 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -19008,7 +19005,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -19033,7 +19030,7 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -19058,7 +19055,7 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -19083,7 +19080,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -19108,7 +19105,7 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -19133,7 +19130,7 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -19158,7 +19155,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -19183,7 +19180,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -19208,7 +19205,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -19233,7 +19230,7 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -19258,7 +19255,7 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -19283,7 +19280,7 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -19308,7 +19305,7 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -19333,7 +19330,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -19358,7 +19355,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -19383,7 +19380,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -19408,7 +19405,7 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -19433,7 +19430,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -19458,7 +19455,7 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -19483,7 +19480,7 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -19508,7 +19505,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -19533,7 +19530,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -19558,7 +19555,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -19583,7 +19580,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -19608,7 +19605,7 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -19633,7 +19630,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -19658,7 +19655,7 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -19683,7 +19680,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -19708,7 +19705,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -19733,7 +19730,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -19758,7 +19755,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -19783,7 +19780,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -19808,7 +19805,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -19833,7 +19830,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -19858,7 +19855,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -19883,7 +19880,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -19908,7 +19905,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -19933,7 +19930,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -19958,7 +19955,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -19983,7 +19980,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -20008,7 +20005,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -20033,7 +20030,7 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -20058,7 +20055,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -20083,7 +20080,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -20108,7 +20105,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -20133,7 +20130,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>箱</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
